--- a/cet4/result/43_农业女神_科技兴农的逆袭路/43_农业女神_科技兴农的逆袭路_学习版.xlsx
+++ b/cet4/result/43_农业女神_科技兴农的逆袭路/43_农业女神_科技兴农的逆袭路_学习版.xlsx
@@ -397,941 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Monday</v>
       </c>
       <c r="B2" t="str">
-        <v>Monday</v>
+        <v>/ˈmʌndeɪ,ˈmʌndi/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>星期一</v>
       </c>
-      <c r="D2" t="str">
-        <v>Monday(星期一)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>Asia</v>
       </c>
       <c r="B3" t="str">
-        <v>Asia</v>
+        <v>/ˈeɪʒə/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>亚洲</v>
       </c>
-      <c r="D3" t="str">
-        <v>Asia(亚洲)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>executive</v>
       </c>
       <c r="B4" t="str">
-        <v>executive</v>
+        <v>/ɪɡˈzekjətɪv/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>行政主管</v>
       </c>
-      <c r="D4" t="str">
-        <v>executive(行政主管)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>ought</v>
       </c>
       <c r="B5" t="str">
-        <v>ought</v>
+        <v>/ɔːt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./pron.</v>
+      </c>
+      <c r="D5" t="str">
         <v>应该</v>
       </c>
-      <c r="D5" t="str">
-        <v>ought(应该)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>concrete</v>
       </c>
       <c r="B6" t="str">
-        <v>concrete</v>
+        <v>/ˈkɑːnkriːt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>具体的</v>
       </c>
-      <c r="D6" t="str">
-        <v>concrete(具体的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>long</v>
       </c>
       <c r="B7" t="str">
-        <v>long</v>
+        <v>/lɔːŋ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vi./v./adj./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>漫长的</v>
       </c>
-      <c r="D7" t="str">
-        <v>long(漫长的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>agriculture</v>
       </c>
       <c r="B8" t="str">
-        <v>agriculture</v>
+        <v>/ˈæɡrɪkʌltʃər/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>农业</v>
       </c>
-      <c r="D8" t="str">
-        <v>agriculture(农业)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>them</v>
       </c>
       <c r="B9" t="str">
-        <v>them</v>
+        <v>/ðəm; ðem/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D9" t="str">
         <v>他们</v>
       </c>
-      <c r="D9" t="str">
-        <v>them(他们)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>walk</v>
       </c>
       <c r="B10" t="str">
-        <v>walk</v>
+        <v>/wɔːk/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>步行</v>
       </c>
-      <c r="D10" t="str">
-        <v>walk(步行)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>rough</v>
       </c>
       <c r="B11" t="str">
-        <v>rough</v>
+        <v>/rʌf/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>崎岖的</v>
       </c>
-      <c r="D11" t="str">
-        <v>rough(崎岖的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>highly</v>
       </c>
       <c r="B12" t="str">
-        <v>highly</v>
+        <v>/ˈhaɪli/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>高度地</v>
       </c>
-      <c r="D12" t="str">
-        <v>highly(高度地)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>bridge</v>
       </c>
       <c r="B13" t="str">
-        <v>bridge</v>
+        <v>/brɪdʒ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>跨越</v>
       </c>
-      <c r="D13" t="str">
-        <v>bridge(跨越)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>task</v>
       </c>
       <c r="B14" t="str">
-        <v>task</v>
+        <v>/tæsk/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>任务</v>
       </c>
-      <c r="D14" t="str">
-        <v>task(任务)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>dairy</v>
       </c>
       <c r="B15" t="str">
-        <v>dairy</v>
+        <v>/ˈderi/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>乳制品</v>
       </c>
-      <c r="D15" t="str">
-        <v>dairy(乳制品)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>sometimes</v>
       </c>
       <c r="B16" t="str">
-        <v>sometimes</v>
+        <v>/ˈsʌmtaɪmz/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D16" t="str">
         <v>有时</v>
       </c>
-      <c r="D16" t="str">
-        <v>sometimes(有时)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>fetch</v>
       </c>
       <c r="B17" t="str">
-        <v>fetch</v>
+        <v>/fetʃ/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>取来</v>
       </c>
-      <c r="D17" t="str">
-        <v>fetch(取来)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>bleed</v>
       </c>
       <c r="B18" t="str">
-        <v>bleed</v>
+        <v>/bliːd/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>流血</v>
       </c>
-      <c r="D18" t="str">
-        <v>bleed(流血)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>wrist</v>
       </c>
       <c r="B19" t="str">
-        <v>wrist</v>
+        <v>/rɪst/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>手腕</v>
       </c>
-      <c r="D19" t="str">
-        <v>wrist(手腕)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>gallon</v>
       </c>
       <c r="B20" t="str">
-        <v>gallon</v>
+        <v>/ˈɡælən/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>加仑</v>
       </c>
-      <c r="D20" t="str">
-        <v>gallon(加仑)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>deaf</v>
       </c>
       <c r="B21" t="str">
-        <v>deaf</v>
+        <v>/def/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>聋的</v>
       </c>
-      <c r="D21" t="str">
-        <v>deaf(聋的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>mention</v>
       </c>
       <c r="B22" t="str">
-        <v>them</v>
+        <v>/ˈmenʃn/</v>
       </c>
       <c r="C22" t="str">
-        <v>他们</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>them(他们)📢</v>
+        <v>提及</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>safety</v>
       </c>
       <c r="B23" t="str">
-        <v>mention</v>
+        <v>/ˈseɪfti/</v>
       </c>
       <c r="C23" t="str">
-        <v>提及</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>mention(提及)📢</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>will</v>
       </c>
       <c r="B24" t="str">
-        <v>safety</v>
+        <v>/wɪl/</v>
       </c>
       <c r="C24" t="str">
-        <v>安全性</v>
+        <v>n./v./aux.</v>
       </c>
       <c r="D24" t="str">
-        <v>safety(安全性)📢</v>
+        <v>将要</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>super</v>
       </c>
       <c r="B25" t="str">
-        <v>will</v>
+        <v>/ˈsuːpər/</v>
       </c>
       <c r="C25" t="str">
-        <v>将要</v>
+        <v>n./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>will(将要)📢</v>
+        <v>超级的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>senate</v>
       </c>
       <c r="B26" t="str">
-        <v>super</v>
+        <v>/ˈsenət/</v>
       </c>
       <c r="C26" t="str">
-        <v>超级的</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>super(超级的)📢</v>
+        <v>参议院</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>colleague</v>
       </c>
       <c r="B27" t="str">
-        <v>senate</v>
+        <v>/ˈkɑːliːɡ/</v>
       </c>
       <c r="C27" t="str">
-        <v>参议院</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>senate(参议院)📢</v>
+        <v>同事</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>picnic</v>
       </c>
       <c r="B28" t="str">
-        <v>them</v>
+        <v>/ˈpɪknɪk/</v>
       </c>
       <c r="C28" t="str">
-        <v>他们</v>
+        <v>n./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>them(他们)📢</v>
+        <v>野餐</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>publication</v>
       </c>
       <c r="B29" t="str">
-        <v>colleague</v>
+        <v>/ˌpʌblɪˈkeɪʃn/</v>
       </c>
       <c r="C29" t="str">
-        <v>同事</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>colleague(同事)📢</v>
+        <v>出版物</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>republican</v>
       </c>
       <c r="B30" t="str">
-        <v>picnic</v>
+        <v>/rɪˈpʌblɪkən/</v>
       </c>
       <c r="C30" t="str">
-        <v>野餐</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>picnic(野餐)📢</v>
+        <v>共和国的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>remark</v>
       </c>
       <c r="B31" t="str">
-        <v>publication</v>
+        <v>/rɪˈmɑːrk/</v>
       </c>
       <c r="C31" t="str">
-        <v>出版物</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>publication(出版物)📢</v>
+        <v>评论</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rabbit</v>
       </c>
       <c r="B32" t="str">
-        <v>republican</v>
+        <v>/ˈræbɪt/</v>
       </c>
       <c r="C32" t="str">
-        <v>共和国的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>republican(共和国的)📢</v>
+        <v>兔子</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>wipe</v>
       </c>
       <c r="B33" t="str">
-        <v>remark</v>
+        <v>/waɪp/</v>
       </c>
       <c r="C33" t="str">
-        <v>评论</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>remark(评论)📢</v>
+        <v>擦拭</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>swing</v>
       </c>
       <c r="B34" t="str">
-        <v>super</v>
+        <v>/swɪŋ/</v>
       </c>
       <c r="C34" t="str">
-        <v>极好的</v>
+        <v>n./v.</v>
       </c>
       <c r="D34" t="str">
-        <v>super(极好的)📢</v>
+        <v>秋千</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>roast</v>
       </c>
       <c r="B35" t="str">
-        <v>rabbit</v>
+        <v>/roʊst/</v>
       </c>
       <c r="C35" t="str">
-        <v>兔子</v>
+        <v>v.</v>
       </c>
       <c r="D35" t="str">
-        <v>rabbit(兔子)📢</v>
+        <v>烤</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>opportunity</v>
       </c>
       <c r="B36" t="str">
-        <v>wipe</v>
+        <v>/ˌɑːpərˈtuːnəti/</v>
       </c>
       <c r="C36" t="str">
-        <v>擦拭</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>wipe(擦拭)📢</v>
+        <v>机会</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>formation</v>
       </c>
       <c r="B37" t="str">
-        <v>swing</v>
+        <v>/fɔːrˈmeɪʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>秋千</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>swing(秋千)📢</v>
+        <v>形成</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>mail</v>
       </c>
       <c r="B38" t="str">
-        <v>roast</v>
+        <v>/meɪl/</v>
       </c>
       <c r="C38" t="str">
-        <v>烤</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>roast(烤)📢</v>
+        <v>邮件</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>but</v>
       </c>
       <c r="B39" t="str">
-        <v>opportunity</v>
+        <v>/bʌt/</v>
       </c>
       <c r="C39" t="str">
-        <v>机会</v>
+        <v>n./v./adv./prep./conj.</v>
       </c>
       <c r="D39" t="str">
-        <v>opportunity(机会)📢</v>
+        <v>但是</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>bee</v>
       </c>
       <c r="B40" t="str">
-        <v>formation</v>
+        <v>/biː/</v>
       </c>
       <c r="C40" t="str">
-        <v>形成</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>formation(形成)📢</v>
+        <v>蜜蜂</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>ankle</v>
       </c>
       <c r="B41" t="str">
-        <v>mail</v>
+        <v>/ˈæŋkl/</v>
       </c>
       <c r="C41" t="str">
-        <v>邮件</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>mail(邮件)📢</v>
+        <v>脚踝</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>dash</v>
       </c>
       <c r="B42" t="str">
-        <v>but</v>
+        <v>/dæʃ/</v>
       </c>
       <c r="C42" t="str">
-        <v>但是</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>but(但是)📢</v>
+        <v>猛冲</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>congratulation</v>
       </c>
       <c r="B43" t="str">
-        <v>concrete</v>
+        <v>/kənˌɡrætʃuˈleɪʃn/</v>
       </c>
       <c r="C43" t="str">
-        <v>混凝土</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>concrete(混凝土)📢</v>
+        <v>祝贺</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>twelfth</v>
       </c>
       <c r="B44" t="str">
-        <v>bee</v>
+        <v>/twelfθ/</v>
       </c>
       <c r="C44" t="str">
-        <v>蜜蜂</v>
+        <v>n./adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>bee(蜜蜂)📢</v>
+        <v>第十二</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>news</v>
       </c>
       <c r="B45" t="str">
-        <v>ankle</v>
+        <v>/nuːz/</v>
       </c>
       <c r="C45" t="str">
-        <v>脚踝</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>ankle(脚踝)📢</v>
+        <v>新闻</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>use</v>
       </c>
       <c r="B46" t="str">
-        <v>dash</v>
+        <v>/juːz/</v>
       </c>
       <c r="C46" t="str">
-        <v>猛冲</v>
+        <v>n./vt.</v>
       </c>
       <c r="D46" t="str">
-        <v>dash(猛冲)📢</v>
+        <v>用途</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>disguise</v>
       </c>
       <c r="B47" t="str">
-        <v>will</v>
+        <v>/dɪsˈɡaɪz/</v>
       </c>
       <c r="C47" t="str">
-        <v>将要</v>
+        <v>n./vt.</v>
       </c>
       <c r="D47" t="str">
-        <v>will(将要)📢</v>
+        <v>伪装</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>casual</v>
       </c>
       <c r="B48" t="str">
-        <v>congratulation</v>
+        <v>/ˈkæʒuəl/</v>
       </c>
       <c r="C48" t="str">
-        <v>祝贺</v>
+        <v>n./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>congratulation(祝贺)📢</v>
+        <v>随意的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>rib</v>
       </c>
       <c r="B49" t="str">
-        <v>twelfth</v>
+        <v>/rɪb/</v>
       </c>
       <c r="C49" t="str">
-        <v>第十二</v>
+        <v>n./vt.</v>
       </c>
       <c r="D49" t="str">
-        <v>twelfth(第十二)📢</v>
+        <v>肋骨</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>achieve</v>
       </c>
       <c r="B50" t="str">
-        <v>news</v>
+        <v>/əˈtʃiːv/</v>
       </c>
       <c r="C50" t="str">
-        <v>新闻</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>news(新闻)📢</v>
+        <v>实现</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>sign</v>
       </c>
       <c r="B51" t="str">
-        <v>use</v>
+        <v>/saɪn/</v>
       </c>
       <c r="C51" t="str">
-        <v>用途</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>use(用途)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>long</v>
-      </c>
-      <c r="C52" t="str">
-        <v>漫长</v>
-      </c>
-      <c r="D52" t="str">
-        <v>long(漫长)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>republican</v>
-      </c>
-      <c r="C53" t="str">
-        <v>共和国</v>
-      </c>
-      <c r="D53" t="str">
-        <v>republican(共和国)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>disguise</v>
-      </c>
-      <c r="C54" t="str">
-        <v>伪装</v>
-      </c>
-      <c r="D54" t="str">
-        <v>disguise(伪装)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>casual</v>
-      </c>
-      <c r="C55" t="str">
-        <v>随意的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>casual(随意的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Monday</v>
-      </c>
-      <c r="C56" t="str">
-        <v>星期一</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Monday(星期一)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>mail</v>
-      </c>
-      <c r="C57" t="str">
-        <v>信件</v>
-      </c>
-      <c r="D57" t="str">
-        <v>mail(信件)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>opportunity</v>
-      </c>
-      <c r="C58" t="str">
-        <v>机会</v>
-      </c>
-      <c r="D58" t="str">
-        <v>opportunity(机会)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>will</v>
-      </c>
-      <c r="C59" t="str">
-        <v>意志</v>
-      </c>
-      <c r="D59" t="str">
-        <v>will(意志)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>rabbit</v>
-      </c>
-      <c r="C60" t="str">
-        <v>兔子</v>
-      </c>
-      <c r="D60" t="str">
-        <v>rabbit(兔子)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>rib</v>
-      </c>
-      <c r="C61" t="str">
-        <v>肋骨</v>
-      </c>
-      <c r="D61" t="str">
-        <v>rib(肋骨)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>achieve</v>
-      </c>
-      <c r="C62" t="str">
-        <v>实现</v>
-      </c>
-      <c r="D62" t="str">
-        <v>achieve(实现)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>sign</v>
-      </c>
-      <c r="C63" t="str">
         <v>迹象</v>
-      </c>
-      <c r="D63" t="str">
-        <v>sign(迹象)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>publication</v>
-      </c>
-      <c r="C64" t="str">
-        <v>出版物</v>
-      </c>
-      <c r="D64" t="str">
-        <v>publication(出版物)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>twelfth</v>
-      </c>
-      <c r="C65" t="str">
-        <v>第十二</v>
-      </c>
-      <c r="D65" t="str">
-        <v>twelfth(第十二)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>but</v>
-      </c>
-      <c r="C66" t="str">
-        <v>但是</v>
-      </c>
-      <c r="D66" t="str">
-        <v>but(但是)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>